--- a/PMS_UAT_TestCases_Comprehensive.xlsx
+++ b/PMS_UAT_TestCases_Comprehensive.xlsx
@@ -508,98 +508,56 @@
     <t>COMP-026</t>
   </si>
   <si>
-    <t>Section F - Drawings &amp; Manuals - upload document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select a component
-2. View Section F - Drawings &amp; Manuals
-3. Click 'Upload Document' button
-4. Select a PDF file (&lt; 50 MB)
-5. Enter Document Title and Category
-6. Click Upload</t>
-  </si>
-  <si>
-    <t>File: manual.pdf (5 MB), Title: 'Engine Manual v3', Category: 'Technical Manual'</t>
-  </si>
-  <si>
-    <t>Document uploads successfully. Appears in table with columns: Document Title, Category, Actions. Max file size hint: '50MB'. Download and Delete action buttons available.</t>
+    <t>Section D - Maintenance History columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select a component with maintenance records
+2. View Section D - Maintenance History
+3. Verify table columns: WO No, Job Title, Type, Date Completed, Running Hours, Performed By, Approved By, Status</t>
+  </si>
+  <si>
+    <t>Component with completed WOs</t>
+  </si>
+  <si>
+    <t>Table columns: WO No, Job Title, Type, Date Completed, Running Hours, Performed By, Approved By, Status. Record count label: 'X maintenance record(s) found'.</t>
   </si>
   <si>
     <t>COMP-027</t>
   </si>
   <si>
-    <t>Section F - Drawings &amp; Manuals - view and delete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select a component with uploaded drawings
-2. View Section F table with documents
-3. Click View/Download action on a document
-4. Click Delete action on another document
-5. Confirm deletion</t>
-  </si>
-  <si>
-    <t>Component with uploaded documents</t>
-  </si>
-  <si>
-    <t>View opens/downloads the document. Delete removes the document after confirmation. Document count updates.</t>
+    <t>Section D - Click record to view full details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. View Section D records
+2. Note label: 'Click on a record to view full details'
+3. Click on a maintenance history record
+4. Observe detail view opens</t>
+  </si>
+  <si>
+    <t>Completed WO history record</t>
+  </si>
+  <si>
+    <t>Full work order detail opens for the selected maintenance history record. All completion details visible.</t>
   </si>
   <si>
     <t>COMP-028</t>
   </si>
   <si>
-    <t>Section G - Classification &amp; Regulatory Data - view surveys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select a component
-2. View Section G - Classification &amp; Regulatory Data
-3. Verify survey count label 'X survey(s) found'
-4. Review survey table columns</t>
-  </si>
-  <si>
-    <t>Component with survey data</t>
-  </si>
-  <si>
-    <t>Survey table shows columns: Classification Society, Survey Type, Certificate No., Last Survey, Next Due, Status. Count label matches rows.</t>
+    <t>Section D - Records are immutable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. View Section D - Maintenance History
+2. Verify 'Records are immutable' label displayed
+3. Try to edit a history record</t>
+  </si>
+  <si>
+    <t>Any history record</t>
+  </si>
+  <si>
+    <t>Label 'Records are immutable' displayed. No edit buttons on history records. Data is read-only.</t>
   </si>
   <si>
     <t>COMP-029</t>
-  </si>
-  <si>
-    <t>Section G - Classification &amp; Regulatory Data - add survey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select a component
-2. Navigate to Section G
-3. Click 'Add Survey' button
-4. Fill Classification Society, Survey Type, Certificate No., Last Survey Date, Next Due
-5. Click Save</t>
-  </si>
-  <si>
-    <t>Society: DNV GL, Type: Annual, Cert: DNV-2026-001</t>
-  </si>
-  <si>
-    <t>New survey record added. Appears in survey table with correct status. Success message displayed.</t>
-  </si>
-  <si>
-    <t>COMP-030</t>
-  </si>
-  <si>
-    <t>Section H - Requisitions - view linked requisitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select a component
-2. View Section H - Requisitions
-3. Verify requisition count label 'X requisition(s)'
-4. Review requisition table</t>
-  </si>
-  <si>
-    <t>Component with requisitions</t>
-  </si>
-  <si>
-    <t>Requisition table shows columns: Req. No, Item/Service, Qty, Raised On, Priority, Status. Linked procurement requests for the component displayed.</t>
-  </si>
-  <si>
-    <t>COMP-031</t>
   </si>
   <si>
     <t>Section E - Spares table columns verification</t>
@@ -614,6 +572,40 @@
   </si>
   <si>
     <t>Table columns: Part Code, Part Name, Critical (badge), ROB, Min, Stock (status badge), Location (popover), IHM indicator.</t>
+  </si>
+  <si>
+    <t>COMP-030</t>
+  </si>
+  <si>
+    <t>Section E - Stock status badges in spares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. View Section E spares list
+2. Check stock status badges for each spare
+3. Verify color coding</t>
+  </si>
+  <si>
+    <t>Spares with various stock levels</t>
+  </si>
+  <si>
+    <t>Stock column shows badges: Green (OK), Orange (At Min), Red (Low/Critical). Badge color matches ROB vs Min comparison.</t>
+  </si>
+  <si>
+    <t>COMP-031</t>
+  </si>
+  <si>
+    <t>Section E - Location popover for spare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. View Section E spares
+2. Click Location column popover for a spare
+3. View location-specific stock breakdown</t>
+  </si>
+  <si>
+    <t>Spare with multiple locations</t>
+  </si>
+  <si>
+    <t>Popover opens showing stock quantity per location (Location A, Location B). Total matches ROB column.</t>
   </si>
   <si>
     <t>COMP-032</t>
@@ -10677,7 +10669,7 @@
         <v>153</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>154</v>
@@ -10715,7 +10707,7 @@
         <v>158</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>159</v>
@@ -10753,7 +10745,7 @@
         <v>163</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>164</v>
